--- a/в бланки заводов/ПОКОМ КИ/pokom_ki/чистый бланк/старые/2026/10,26/Бланк КИ  клиент ООО НВ на отгрузку с 12.10.2026.xlsx
+++ b/в бланки заводов/ПОКОМ КИ/pokom_ki/чистый бланк/старые/2026/10,26/Бланк КИ  клиент ООО НВ на отгрузку с 12.10.2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Uaer4\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB60593B-534C-47CF-A593-080B875D9C38}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA0AA8FA-0C89-4043-8640-BDDB23954CD3}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
